--- a/配置核查表_v2.0.0_标注自动验证.xlsx
+++ b/配置核查表_v2.0.0_标注自动验证.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22480" windowHeight="10780" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17775" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -631,24 +631,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -657,15 +649,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1257,17 +1245,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N139"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.73076923076923" defaultRowHeight="16.8"/>
+  <dimension ref="A1:M139"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.733333333333331" defaultRowHeight="13.5"/>
   <cols>
-    <col width="23.3076923076923" customWidth="1" style="11" min="1" max="1"/>
-    <col width="86.95192307692309" customWidth="1" style="11" min="2" max="2"/>
-    <col width="11.0865384615385" customWidth="1" style="11" min="4" max="4"/>
-    <col width="9.45192307692308" customWidth="1" style="11" min="6" max="6"/>
+    <col width="23.3083333333333" customWidth="1" style="1" min="1" max="1"/>
+    <col width="86.95" customWidth="1" style="1" min="2" max="2"/>
+    <col width="11.0833333333333" customWidth="1" style="1" min="4" max="4"/>
+    <col width="9.449999999999999" customWidth="1" style="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="187" customHeight="1" s="11">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="187" customHeight="1" s="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>本表填写说明及作业指导书要求：
 1、若某个检查项适用于右侧的检查对象，则在对应检查项行、对应检查项列打“勾”；缺乏资料尚未完成核查，对应项空白；经验证无需核查的项打“—”
@@ -1306,64 +1294,59 @@
           <t>数据库</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>工具自动验证</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1" s="11">
-      <c r="C3" s="4" t="inlineStr">
+    <row r="3" ht="34" customHeight="1" s="1">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Windows7</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>WindowsXP</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>中标麒麟</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>银河麒麟</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Nginx</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Tomocat</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>SQLSever</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>达梦</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>redis</t>
         </is>
@@ -1375,7 +1358,7 @@
           <t>系统安全</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>1、操作系统、数据管理系统、中间件等平台软件应及时安装补丁程序</t>
         </is>
@@ -1430,19 +1413,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="M4" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>2、操作系统应安装防病毒软件并及时升级</t>
         </is>
@@ -1497,19 +1475,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M5" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>3、操作系统应按需求裁剪服务和端口</t>
         </is>
@@ -1564,19 +1537,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="M6" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>4、操作系应身有防火墙功能</t>
         </is>
@@ -1631,19 +1599,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="M7" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>5、操作系统应停用冗余网络设置</t>
         </is>
@@ -1658,8 +1621,16 @@
           <t>√</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>—</t>
@@ -1690,19 +1661,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="M8" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" s="11">
-      <c r="B9" s="8" t="inlineStr">
+    <row r="9" ht="34" customHeight="1" s="1">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>6、操作系统远程管理应开放唯一管理服务,指定管理终端
 并采取传输加密保护措施</t>
@@ -1758,19 +1724,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="M9" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" s="11">
-      <c r="B10" s="8" t="inlineStr">
+    <row r="10" ht="34" customHeight="1" s="1">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>7、数据库管理系统应删除冗余帐户,应设置不少于8个字符且字符采用字母大小写，
 数字及特殊字符混合编制的账户口令</t>
@@ -1826,19 +1787,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="M10" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>8、数据库管理系统应删除冗余存储过程</t>
         </is>
@@ -1893,19 +1849,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="M11" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>9、数据库管理系统应具有基于表级增删改查等细粒度访问和管理授权功能</t>
         </is>
@@ -1955,20 +1906,19 @@
           <t>√</t>
         </is>
       </c>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>10、数据库管理系统应具有自主访问控制功能</t>
         </is>
@@ -2023,19 +1973,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="M13" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>11、数据库管理系统应具有备份和恢复功能</t>
         </is>
@@ -2090,19 +2035,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="M14" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>12、数据库管理系统应具有表级审计、告警和阻断功能</t>
         </is>
@@ -2157,19 +2097,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="M15" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>13、数据库管理系统的数据应和其它应用的数据分类独立存储</t>
         </is>
@@ -2219,20 +2154,19 @@
           <t>√</t>
         </is>
       </c>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="M16" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>14、中间件应采取限制运行权限和使用安全管理通道等安全加固措施</t>
         </is>
@@ -2287,19 +2221,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="M17" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>15、应具备数据库管理系统超级管理员远程登录限制远程登陆限制能力</t>
         </is>
@@ -2354,19 +2283,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="M18" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>16、应具备数据库管理系统输入（参数）检查能力</t>
         </is>
@@ -2421,27 +2345,38 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="M19" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>17、应限制操作系统开放的远程管理服务或端口</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
           <t>—</t>
@@ -2472,19 +2407,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="M20" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>18、应限制用户对服务器资源的最大或最小使用限度</t>
         </is>
@@ -2499,8 +2429,16 @@
           <t>√</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>—</t>
@@ -2531,19 +2469,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="M21" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>19、应更换数据库管理系统的默认服务端口、管理员用户名和口令</t>
         </is>
@@ -2598,19 +2531,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="M22" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>20、数据库管理系统应配置安全策略</t>
         </is>
@@ -2650,7 +2578,11 @@
           <t>√</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
           <t>√</t>
@@ -2661,19 +2593,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="M23" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>21、数据库管理系统应具有行级或列级审计功能</t>
         </is>
@@ -2728,19 +2655,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="M24" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>22、数据库管理系统应采取单独、安全监控、审计指施</t>
         </is>
@@ -2795,19 +2717,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="M25" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>23、数据库管理系统仅为应用服务器提供访问服务</t>
         </is>
@@ -2862,19 +2779,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="M26" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>24、应具备日志审计能力，审计日志至少保留180天</t>
         </is>
@@ -2924,20 +2836,19 @@
           <t>√</t>
         </is>
       </c>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="M27" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>25、检查是否具备边界保护能力,是否可以抗攻击，防纂改</t>
         </is>
@@ -2992,19 +2903,14 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="M28" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>26、检查是否有防病毒日志、补丁日志、记录相关信息 记录信息的完整，有效</t>
         </is>
@@ -3059,24 +2965,19 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="M29" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="17" customHeight="1" s="11">
+    <row r="30" ht="17" customHeight="1" s="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>数据安全</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>1、集中存储的涉密数据应采取加密保护措施</t>
         </is>
@@ -3131,19 +3032,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="M30" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>2、用户计算机之间的数据交互、文件传输凳应统一管控和审计</t>
         </is>
@@ -3198,19 +3094,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="M31" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>3、涉密存储载体在降密级使用前或重大JS演训活动结束后，应采取数据写覆盖方法及时清除数据</t>
         </is>
@@ -3265,19 +3156,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="M32" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>4、对确定销毁的涉密载体，应采取消磁、粉碎、溶解、化浆和熔化等方法进行销毁</t>
         </is>
@@ -3332,19 +3218,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="M33" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="34" customHeight="1" s="11">
-      <c r="B34" s="8" t="inlineStr">
+    <row r="34" ht="34" customHeight="1" s="1">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>5、网络、系统、应用和用户行为等日志应采取读写控制、加密、变换、完整性校验等保护措施，TM级数据存储1应采取加密保护措施</t>
         </is>
@@ -3399,19 +3280,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="M34" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>6、网络边界应具备信息过滤、敏感内容识别等数据放泄漏能力</t>
         </is>
@@ -3466,19 +3342,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="M35" s="0" t="inlineStr">
         <is>
           <t>跳过（不适用）</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="34" customHeight="1" s="11">
-      <c r="B36" s="8" t="inlineStr">
+    <row r="36" ht="34" customHeight="1" s="1">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>7、数据存储系统管理登录至少采取验证码等增强措施，修改默认用户名和口令等默认设置，管理与访问应具有行为审计功能，审计日志应至少保留180天</t>
         </is>
@@ -3533,19 +3404,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="M36" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>8、数据存储系统应根据重要程度划分不同存储区快，并设置用户访问权限</t>
         </is>
@@ -3600,19 +3466,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="M37" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="34" customHeight="1" s="11">
-      <c r="B38" s="8" t="inlineStr">
+    <row r="38" ht="34" customHeight="1" s="1">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>9、检查数据传输过程是否按照要求进行加密，传输路径是否合理，是否统一管控、留有日志记录，是否具有防泄漏措施，是否存在安全风险</t>
         </is>
@@ -3667,19 +3528,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="M38" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>10、检查数据共享是否合理，是否存在安全隐患</t>
         </is>
@@ -3734,19 +3590,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="M39" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>11、检查对数据的访问是否按照权限分级访问，是否对访问行为进行审计</t>
         </is>
@@ -3801,19 +3652,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="M40" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>12、检查数据采集是否超出业务需求范围</t>
         </is>
@@ -3868,19 +3714,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="M41" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>13、检查数据各环节处理是否满足密级相应的保密要求</t>
         </is>
@@ -3935,19 +3776,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="M42" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1" s="11">
-      <c r="B43" s="8" t="inlineStr">
+    <row r="43" ht="34" customHeight="1" s="1">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>14、检查对数据的访问是否按照权限分级访问，是否对访问行为进行审计，对大数据的访问是否提供同一管控和访问控制</t>
         </is>
@@ -4002,12 +3838,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="M43" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
@@ -4019,7 +3850,7 @@
           <t>应用安全</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>1、应用系统软件应采取备份措施</t>
         </is>
@@ -4074,19 +3905,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="M44" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>2、应用系统软件应及时安装补丁程序，且更新所用升级包应经过安全性测试；</t>
         </is>
@@ -4141,19 +3967,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="M45" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>3、需基于可信根对应用系统软件进行可信验证。可信性受到破坏后报警。</t>
         </is>
@@ -4208,19 +4029,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="M46" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>4、提供公共信息服务的服务器应应与涉密信息服务器分设，专用服务器应只提供专用服务。</t>
         </is>
@@ -4275,19 +4091,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="M47" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>5、提供公共信息服务的服务器应具备防DDoS攻击能力</t>
         </is>
@@ -4342,19 +4153,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="M48" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>6、Web应用系统服务器应采取Web防护措施。</t>
         </is>
@@ -4409,19 +4215,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="M49" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>7、网站服务宜以静态页面形式发布；</t>
         </is>
@@ -4476,19 +4277,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="M50" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>8、网站应采取网页放篡改措施，防止对信息内容的非法修改；</t>
         </is>
@@ -4543,19 +4339,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="M51" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>9、Web应用系统应具备防范SQL注入、跨站脚本等攻击能力；</t>
         </is>
@@ -4610,19 +4401,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="M52" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>10、Web应用系统应具备执行代码有效验证能力；</t>
         </is>
@@ -4677,19 +4463,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="M53" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>11、应具备用户授权访问控制能力；</t>
         </is>
@@ -4744,19 +4525,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="M54" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>12、应具备访问应用最大并发会话连接数限制能力；</t>
         </is>
@@ -4811,19 +4587,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M55" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="M55" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>13、业务管理终端专设专用；</t>
         </is>
@@ -4878,19 +4649,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M56" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="M56" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="34" customHeight="1" s="11">
-      <c r="B57" s="8" t="inlineStr">
+    <row r="57" ht="34" customHeight="1" s="1">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>14、应具有基于用户角色的授权访问控制能力，访问控制主体的细粒度达到用户级或进程级，客体的细粒度应达到文件级、表和记录级、字段级；</t>
         </is>
@@ -4945,19 +4711,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M57" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="M57" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>15、文电等文档专用业务处理系统应具有签名验证、密级标识等功能；</t>
         </is>
@@ -5012,19 +4773,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="M58" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>16、远程管理应采取加密保护措施；</t>
         </is>
@@ -5079,19 +4835,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="M59" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="34" customHeight="1" s="11">
-      <c r="B60" s="8" t="inlineStr">
+    <row r="60" ht="34" customHeight="1" s="1">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>17、应支持管理员、安全员、审计员三权分立的职责划分，禁止设立超级管理员，并限制管理员、安全员、审计员的数量；</t>
         </is>
@@ -5146,19 +4897,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="M60" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>18、业务管理终端登录应采取网络地址限制措施；</t>
         </is>
@@ -5213,19 +4959,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="M61" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>19、应具有结束会话、限定登录错误次数和自动退出等登录失败处理功能；</t>
         </is>
@@ -5280,19 +5021,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M62" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="M62" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>20、宜使用自主设计开发的网络服务、协议、接口等，增强应用安全。</t>
         </is>
@@ -5347,19 +5083,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="M63" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="34" customHeight="1" s="11">
-      <c r="B64" s="8" t="inlineStr">
+    <row r="64" ht="34" customHeight="1" s="1">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>21、应具有基于专用物理部件或生物特征多因素的、与JD密码算法相结合的数字证书用户身份认证功能；</t>
         </is>
@@ -5374,8 +5105,16 @@
           <t>√</t>
         </is>
       </c>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n"/>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
           <t>—</t>
@@ -5406,19 +5145,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="M64" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>22、应更改Web应用系统默认服务发布端口；</t>
         </is>
@@ -5473,19 +5207,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="M65" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>23、应分开设置管理端口与应用端口；</t>
         </is>
@@ -5540,19 +5269,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="5" t="inlineStr">
+      <c r="M66" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>24、应用服务和数据存储应部署在不同的服务器上；</t>
         </is>
@@ -5607,19 +5331,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="M67" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="34" customHeight="1" s="11">
-      <c r="B68" s="8" t="inlineStr">
+    <row r="68" ht="34" customHeight="1" s="1">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>25、应具有对所有访问行为和管理行为的日志审计功能，支持多组合查询检索，可读性强，具有解释和展示功能，审计日志应只是保留180d;</t>
         </is>
@@ -5674,19 +5393,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="5" t="inlineStr">
+      <c r="M68" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>26、应经过代码级安全漏洞挖掘；</t>
         </is>
@@ -5741,19 +5455,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="M69" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1" s="11">
-      <c r="B70" s="8" t="inlineStr">
+    <row r="70" ht="16" customHeight="1" s="1">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>27、检查是否具备对人机接口输入、网络通信输入、文件输入的数据进行格式和长度检查的功能；</t>
         </is>
@@ -5808,19 +5517,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="5" t="inlineStr">
+      <c r="M70" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="34" customHeight="1" s="11">
-      <c r="B71" s="8" t="inlineStr">
+    <row r="71" ht="34" customHeight="1" s="1">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>28、检查是否能够有效检测并防御SQL注入、网页篡改、跨站脚本、拒绝服务等应用层攻击；</t>
         </is>
@@ -5875,19 +5579,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="M71" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>29、检查是否具有用户访问权限统一管理功能；</t>
         </is>
@@ -5942,19 +5641,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M72" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="5" t="inlineStr">
+      <c r="M72" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>30、检查是否具备统一管理措施，是否对远程管理进行限制；</t>
         </is>
@@ -6009,19 +5703,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M73" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="5" t="inlineStr">
+      <c r="M73" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>31、检查是否能够设置最大并发会话连接数、会话建立速率、单用户并发会话数；</t>
         </is>
@@ -6076,19 +5765,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="5" t="inlineStr">
+      <c r="M74" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>32、检查所有应用是否具备备份与恢复功能；</t>
         </is>
@@ -6135,19 +5819,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M75" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="5" t="inlineStr">
+      <c r="M75" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>33、检查应用软件是否基于国产自主可控软硬件自主开发</t>
         </is>
@@ -6202,24 +5881,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M76" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="5" t="inlineStr">
+      <c r="M76" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="34" customHeight="1" s="11">
+    <row r="77" ht="34" customHeight="1" s="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
           <t>用户安全</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>1、用户计算机应安装防病毒软件并及时升级，发现病毒应及时查杀，查杀无效时应断开网络并向网络管理部分报备；</t>
         </is>
@@ -6274,19 +5948,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="5" t="inlineStr">
+      <c r="M77" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>2、用户计算机应根据需要安装补丁程序；</t>
         </is>
@@ -6341,19 +6010,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M78" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="5" t="inlineStr">
+      <c r="M78" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="0" t="inlineStr">
         <is>
           <t>3、用户应设置用户应用口令，通过认证后使用信息服务；</t>
         </is>
@@ -6408,19 +6072,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M79" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="5" t="inlineStr">
+      <c r="M79" s="0" t="inlineStr">
         <is>
           <t>跳过（不适用）</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>4、用户计算机应具有互不相同的用户名和口令；</t>
         </is>
@@ -6475,19 +6134,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M80" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="5" t="inlineStr">
+      <c r="M80" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" s="0" t="inlineStr">
         <is>
           <t>5、用户计算机应关闭冗余系统服务和端口；</t>
         </is>
@@ -6542,19 +6196,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="5" t="inlineStr">
+      <c r="M81" s="0" t="inlineStr">
         <is>
           <t>部分可自动化</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t>6、用户计算机应具备阻断和告警非法连接互联网的能力；</t>
         </is>
@@ -6609,19 +6258,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M82" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="5" t="inlineStr">
+      <c r="M82" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="0" t="inlineStr">
         <is>
           <t>7、用户计算机应具有文件保护功能；</t>
         </is>
@@ -6676,19 +6320,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M83" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="5" t="inlineStr">
+      <c r="M83" s="0" t="inlineStr">
         <is>
           <t>跳过（不适用）</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="34" customHeight="1" s="11">
-      <c r="B84" s="8" t="inlineStr">
+    <row r="84" ht="34" customHeight="1" s="1">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>8、应采取终端管控措施、具有统一配置、安全加固、网络访问控制、外设接口管控、软件进程管控、无线模块禁用、防止IP地址和MAC地址非授权改动等功能；</t>
         </is>
@@ -6743,19 +6382,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N84" s="5" t="inlineStr">
+      <c r="M84" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" s="0" t="inlineStr">
         <is>
           <t>9、用户计算机应禁止安装与工作无关的软件；</t>
         </is>
@@ -6810,19 +6444,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M85" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N85" s="5" t="inlineStr">
+      <c r="M85" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="0" t="inlineStr">
         <is>
           <t>10、用户计算机USB接口应禁止私自连接对拷线和手机、媒体播放设备等个人移动电子设备；</t>
         </is>
@@ -6877,25 +6506,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M86" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N86" s="5" t="inlineStr">
+      <c r="M86" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="51" customHeight="1" s="11">
-      <c r="B87" s="8" t="inlineStr">
+    <row r="87" ht="51" customHeight="1" s="1">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>11、用户计算机登录应使用基于专用物理部件或生物特征的多因素身份认证方式，应设置超时锁屏，屏幕保护等待时间不超过5min,服务器应设置登录口令，口令超度不得少于10个字符，字符应采用字母大小写、数字及特殊字符混合编制，更换周期不超过30d;</t>
         </is>
       </c>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
           <t>√</t>
@@ -6936,19 +6568,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M87" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N87" s="5" t="inlineStr">
+      <c r="M87" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="34" customHeight="1" s="11">
-      <c r="B88" s="8" t="inlineStr">
+    <row r="88" ht="34" customHeight="1" s="1">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>12、用户计算机应物理拆除Wi-Fi、红外、蓝牙等无线模块，确需使用Wi-Fi的应严格采用JY密码等措施保护；</t>
         </is>
@@ -7003,19 +6630,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M88" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N88" s="5" t="inlineStr">
+      <c r="M88" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="0" t="inlineStr">
         <is>
           <t>13、用户计算机应采取非法外联阻断、文件输出管控等措施；</t>
         </is>
@@ -7070,19 +6692,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M89" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N89" s="5" t="inlineStr">
+      <c r="M89" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" s="0" t="inlineStr">
         <is>
           <t>14、应具备用户行为审计能力；审计日志应至少保留xxd；</t>
         </is>
@@ -7137,27 +6754,38 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M90" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N90" s="5" t="inlineStr">
+      <c r="M90" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="0" t="inlineStr">
         <is>
           <t>15、检查安全策略配置情况和设置功能；</t>
         </is>
       </c>
-      <c r="C91" s="3" t="n"/>
-      <c r="D91" s="3" t="n"/>
-      <c r="E91" s="3" t="n"/>
-      <c r="F91" s="3" t="n"/>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
           <t>—</t>
@@ -7188,19 +6816,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M91" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N91" s="5" t="inlineStr">
+      <c r="M91" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="13" customHeight="1" s="11">
-      <c r="B92" s="5" t="inlineStr">
+    <row r="92" ht="13" customHeight="1" s="1">
+      <c r="B92" s="0" t="inlineStr">
         <is>
           <t>16、检查被试装备中操作系统、数据库以及应用软件等是否完成补丁修复和升级到最新版本；</t>
         </is>
@@ -7255,24 +6878,19 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M92" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N92" s="5" t="inlineStr">
+      <c r="M92" s="0" t="inlineStr">
         <is>
           <t>可自动化</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="118" customHeight="1" s="11">
+    <row r="93" ht="118" customHeight="1" s="1">
       <c r="A93" s="3" t="inlineStr">
         <is>
           <t>网络安全</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>1、JD网络跨网跨域数据交换时应按以下流程进行：
 1）应向网络管理部门和主管保密部门提出申请，审批通过后开展工作；
@@ -7332,19 +6950,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M93" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N93" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="152" customHeight="1" s="11">
-      <c r="B94" s="8" t="inlineStr">
+      <c r="M93" s="0" t="inlineStr">
+        <is>
+          <t>需人工（台账/平台核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="152" customHeight="1" s="1">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>2、利用无线网络技术构建安全防护等级为三级、四级、五级的网络时，应按照4.3.3 b 所述工作流程执行：
 1）应向网络管理部门和主管保密部门提出申请，审批通过后开展工作；
@@ -7406,19 +7019,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M94" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N94" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="34" customHeight="1" s="11">
-      <c r="B95" s="8" t="inlineStr">
+      <c r="M94" s="0" t="inlineStr">
+        <is>
+          <t>需人工（台账/平台核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="34" customHeight="1" s="1">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>3、应按最小化原则设计网络架构，局域网宜采用交换技术组网，在适当预留扩展空间的前提下合理配置连续IP地址</t>
         </is>
@@ -7473,19 +7081,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M95" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N95" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="34" customHeight="1" s="11">
-      <c r="B96" s="8" t="inlineStr">
+      <c r="M95" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="34" customHeight="1" s="1">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>4、网络边界物理互联的节点数量、使用的路由协议种类、用于路由的地址网段等应满足最小化原则</t>
         </is>
@@ -7540,19 +7143,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N96" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="34" customHeight="1" s="11">
-      <c r="B97" s="8" t="inlineStr">
+      <c r="M96" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="34" customHeight="1" s="1">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>5、局域网内部应根据业务性质划分若干个安全区域，不同用途的服务器、数据存储设备、除网络设备外的嵌入式设备应单独划分安全区域</t>
         </is>
@@ -7607,19 +7205,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N97" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="34" customHeight="1" s="11">
-      <c r="B98" s="8" t="inlineStr">
+      <c r="M97" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="34" customHeight="1" s="1">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>6、网络设备应根据实际业务需求和安全防护要求按照最小化原则在远程管理、账户设置、访问控制等方面进行安全配置</t>
         </is>
@@ -7674,19 +7267,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N98" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M98" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>7、网络设备应开放唯一网络管理服务，并限制管理终端访问</t>
         </is>
@@ -7741,19 +7329,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M99" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N99" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M99" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" s="0" t="inlineStr">
         <is>
           <t>8、远程网络管理网络设备和网络安全防护设备应采用具有加密保护功能的管理服务</t>
         </is>
@@ -7808,19 +7391,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N100" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M100" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" s="0" t="inlineStr">
         <is>
           <t>9、同一网络传输链路具有相同安全功能的防护设备应使用不同架构或不同品牌产品</t>
         </is>
@@ -7875,19 +7453,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N101" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M101" s="0" t="inlineStr">
+        <is>
+          <t>部分可自动化（脚本+台账）</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>10、应对组播源、组播地址、组播成员采取控制措施</t>
         </is>
@@ -7942,19 +7515,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N102" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M102" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
         <is>
           <t>11、重要网络设备和网络安全防护设备应有备份</t>
         </is>
@@ -8009,19 +7577,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M103" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N103" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M103" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="5" t="inlineStr">
+      <c r="B104" s="0" t="inlineStr">
         <is>
           <t>12、远程传输应采取链路加密、网络加密、信源加密中两层保护措施</t>
         </is>
@@ -8076,19 +7639,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M104" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N104" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="34" customHeight="1" s="11">
-      <c r="B105" s="8" t="inlineStr">
+      <c r="M104" s="0" t="inlineStr">
+        <is>
+          <t>需人工（台账/平台核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="34" customHeight="1" s="1">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>13、应设立网络安全管理中心并指定管理终端，对网络设备、网络安全防护设备、存储设备等资源进行单独管理</t>
         </is>
@@ -8143,19 +7701,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M105" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N105" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="34" customHeight="1" s="11">
-      <c r="B106" s="8" t="inlineStr">
+      <c r="M105" s="0" t="inlineStr">
+        <is>
+          <t>需人工（台账/平台核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="34" customHeight="1" s="1">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>14、与互联网、非JD网络、安全防护等级为一级的网络应物理隔离，与安全防护等级为二级、三级和四级的网络应逻辑隔离</t>
         </is>
@@ -8210,19 +7763,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M106" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N106" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="51" customHeight="1" s="11">
-      <c r="B107" s="8" t="inlineStr">
+      <c r="M106" s="0" t="inlineStr">
+        <is>
+          <t>需人工（台账/平台核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="51" customHeight="1" s="1">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>15、不同用途、不同性质的网络之间应需通过防火墙、网络隔离器、单向传输设备、单项导入设备等网络安全防护设备加强逻辑隔离，应采取边界数据交换控制措施，应具备对攻击行为和非法访问等实时告警、审计、阻断和定位等能力</t>
         </is>
@@ -8277,19 +7825,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M107" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N107" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="34" customHeight="1" s="11">
-      <c r="B108" s="8" t="inlineStr">
+      <c r="M107" s="0" t="inlineStr">
+        <is>
+          <t>需人工（台账/平台核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="34" customHeight="1" s="1">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>16、局域网各安全区域之间、服务器与终端之间、服务器之间、终端之间应采取全网细粒度访问控制措施</t>
         </is>
@@ -8344,19 +7887,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M108" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N108" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M108" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B109" s="0" t="inlineStr">
         <is>
           <t>17、远程传输租用地方线路时应采取链路加密、网络加密、信源加密三层保护措施</t>
         </is>
@@ -8411,19 +7949,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M109" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N109" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="34" customHeight="1" s="11">
-      <c r="B110" s="8" t="inlineStr">
+      <c r="M109" s="0" t="inlineStr">
+        <is>
+          <t>需人工（台账/平台核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="34" customHeight="1" s="1">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>18、应采取不低于基于801.1x协议认证强度的接入认证措施，认证因素至少包括交换机端口、计算机IP地址和MAC地址</t>
         </is>
@@ -8478,19 +8011,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M110" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N110" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M110" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" s="0" t="inlineStr">
         <is>
           <t>19、用户计算机之间应逻辑隔离</t>
         </is>
@@ -8545,19 +8073,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M111" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N111" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M111" s="0" t="inlineStr">
+        <is>
+          <t>可自动化（网络设备脚本）</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="5" t="inlineStr">
+      <c r="B112" s="0" t="inlineStr">
         <is>
           <t>20、应具备全网行为审计记录能力，审计日志应至少保留180天</t>
         </is>
@@ -8612,19 +8135,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M112" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N112" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M112" s="0" t="inlineStr">
+        <is>
+          <t>需人工（台账/平台核查）</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" s="0" t="inlineStr">
         <is>
           <t>21、应对全网攻击行为、违规行为采取实时监视、报警、审计、控制处理、阻断和定位措施</t>
         </is>
@@ -8679,19 +8197,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M113" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N113" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M113" s="0" t="inlineStr">
+        <is>
+          <t>需人工（台账/平台核查）</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>22、数据存储系统的管理网路与应用网路应逻辑隔离</t>
         </is>
@@ -8746,19 +8259,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M114" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N114" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
+      <c r="M114" s="0" t="inlineStr">
+        <is>
+          <t>部分可自动化（脚本+台账）</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B115" s="0" t="inlineStr">
         <is>
           <t>23、检查网络设备配备的合理性、必要性，是否存在非必要的冗余内容</t>
         </is>
@@ -8813,24 +8321,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M115" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N115" s="5" t="inlineStr">
-        <is>
-          <t>跳过（网络设备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="34" customHeight="1" s="11">
+      <c r="M115" s="0" t="inlineStr">
+        <is>
+          <t>部分可自动化（脚本+台账）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="34" customHeight="1" s="1">
       <c r="A116" s="3" t="inlineStr">
         <is>
           <t>物理安全</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>1、使用的网络设备、服务器、终端等，应选用进入《全J计算机及网络设备集中采购目录》的产品</t>
         </is>
@@ -8885,19 +8388,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M116" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N116" s="5" t="inlineStr">
+      <c r="M116" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B117" s="0" t="inlineStr">
         <is>
           <t>2、使用的安全网关、防火墙等信息安全产品，应通过JD信息安全测评认证机构的认证</t>
         </is>
@@ -8952,19 +8450,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M117" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N117" s="5" t="inlineStr">
+      <c r="M117" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t>3、机房应有序、规范、合理走线布线，明确互联网区域和内部区域，粘贴标识，区分不同线路</t>
         </is>
@@ -9019,19 +8512,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M118" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N118" s="5" t="inlineStr">
+      <c r="M118" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B119" s="0" t="inlineStr">
         <is>
           <t>4、机房应符合GB 2887-2011中4.6.1所规定的温湿度等要求</t>
         </is>
@@ -9086,19 +8574,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M119" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N119" s="5" t="inlineStr">
+      <c r="M119" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="B120" s="5" t="inlineStr">
+      <c r="B120" s="0" t="inlineStr">
         <is>
           <t>5、机房应安装安防监控设备，对机房的人员进出、设备操作等进行监管</t>
         </is>
@@ -9153,19 +8636,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M120" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N120" s="5" t="inlineStr">
+      <c r="M120" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B121" s="0" t="inlineStr">
         <is>
           <t>6、机房应将涉密区域和互联网区域设置于不同场所</t>
         </is>
@@ -9220,19 +8698,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M121" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N121" s="5" t="inlineStr">
+      <c r="M121" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="B122" s="5" t="inlineStr">
+      <c r="B122" s="0" t="inlineStr">
         <is>
           <t>7、在涉密网络中使用过的打印机、复印机、刻录机、扫描仪、存储载体等设备严禁在互联网中使用</t>
         </is>
@@ -9287,19 +8760,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M122" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N122" s="5" t="inlineStr">
+      <c r="M122" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="34" customHeight="1" s="11">
-      <c r="B123" s="8" t="inlineStr">
+    <row r="123" ht="34" customHeight="1" s="1">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>8、应选用《JY关键软硬件自主可控产品名录》中的芯片类、计算机及外设类、网络设备类、安全防护设备类、存储设备类等产品</t>
         </is>
@@ -9354,19 +8822,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M123" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N123" s="5" t="inlineStr">
+      <c r="M123" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="5" t="inlineStr">
+      <c r="B124" s="0" t="inlineStr">
         <is>
           <t>9、与安全防护等级低的网络使用不同色系线缆进行严格隔离区分</t>
         </is>
@@ -9421,12 +8884,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M124" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N124" s="5" t="inlineStr">
+      <c r="M124" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
@@ -9438,7 +8896,7 @@
           <t>组织机构</t>
         </is>
       </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="B125" s="0" t="inlineStr">
         <is>
           <t>1、应设置安全管理机构，保证系统安全措施的落实；</t>
         </is>
@@ -9493,19 +8951,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M125" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N125" s="5" t="inlineStr">
+      <c r="M125" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="5" t="inlineStr">
+      <c r="B126" s="0" t="inlineStr">
         <is>
           <t>2、应配备专职系统安全保密管理人员，负责系统安全措施的落实。</t>
         </is>
@@ -9560,19 +9013,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M126" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N126" s="5" t="inlineStr">
+      <c r="M126" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="5" t="inlineStr">
+      <c r="B127" s="0" t="inlineStr">
         <is>
           <t>3、应具有安全管理领导机构，督导系统安全措施的落实；</t>
         </is>
@@ -9627,19 +9075,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M127" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N127" s="5" t="inlineStr">
+      <c r="M127" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B128" s="0" t="inlineStr">
         <is>
           <t>4、应具有系统安全保密技术管理人员，具体负责安全保密技术措施的落实，保证系统安全运行；</t>
         </is>
@@ -9694,19 +9137,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M128" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N128" s="5" t="inlineStr">
+      <c r="M128" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="B129" s="5" t="inlineStr">
+      <c r="B129" s="0" t="inlineStr">
         <is>
           <t>5、应具有完善的应急响应体系，应对突发事件。</t>
         </is>
@@ -9761,12 +9199,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M129" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N129" s="5" t="inlineStr">
+      <c r="M129" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
@@ -9778,7 +9211,7 @@
           <t>规章制度</t>
         </is>
       </c>
-      <c r="B130" s="5" t="inlineStr">
+      <c r="B130" s="0" t="inlineStr">
         <is>
           <t>1、应具有日常安全管理制度、入网审批制度和系统安全保密检查制度等；</t>
         </is>
@@ -9833,19 +9266,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M130" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N130" s="5" t="inlineStr">
+      <c r="M130" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="B131" s="5" t="inlineStr">
+      <c r="B131" s="0" t="inlineStr">
         <is>
           <t>2、应具有安全管理操作规程、安全监控操作规程、安全审计操作规程、应急响应操作规程等。</t>
         </is>
@@ -9900,19 +9328,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M131" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N131" s="5" t="inlineStr">
+      <c r="M131" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="B132" s="5" t="inlineStr">
+      <c r="B132" s="0" t="inlineStr">
         <is>
           <t>3、应具有日常系统备份制度和存储载体使用管理制度；</t>
         </is>
@@ -9967,19 +9390,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M132" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N132" s="5" t="inlineStr">
+      <c r="M132" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B133" s="0" t="inlineStr">
         <is>
           <t>4、应具有脆弱性分析等规程。</t>
         </is>
@@ -10034,24 +9452,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M133" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N133" s="5" t="inlineStr">
+      <c r="M133" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="34" customHeight="1" s="11">
+    <row r="134" ht="34" customHeight="1" s="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
           <t>管理实施</t>
         </is>
       </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>1、应具有应急响应预案，当发生危及系统安全的事件时应根据操作规程及时采取措施，符合应急预案启动条件时按预案开展应急措施；</t>
         </is>
@@ -10106,19 +9519,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M134" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N134" s="5" t="inlineStr">
+      <c r="M134" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="34" customHeight="1" s="11">
-      <c r="B135" s="8" t="inlineStr">
+    <row r="135" ht="34" customHeight="1" s="1">
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>2、计算机信息系统安全保密管理人员应能对网络中的网络安全防护设备进行统一配置、管理，并能实现安全管理中心与网络安全防护设备之间的响应；</t>
         </is>
@@ -10173,19 +9581,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M135" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N135" s="5" t="inlineStr">
+      <c r="M135" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="B136" s="5" t="inlineStr">
+      <c r="B136" s="0" t="inlineStr">
         <is>
           <t>3、应具有与实际情况相符且完整的安全保密策略文档和安全保密技术及产品配置的详细记录；</t>
         </is>
@@ -10240,19 +9643,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M136" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N136" s="5" t="inlineStr">
+      <c r="M136" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="51" customHeight="1" s="11">
-      <c r="B137" s="8" t="inlineStr">
+    <row r="137" ht="51" customHeight="1" s="1">
+      <c r="B137" s="4" t="inlineStr">
         <is>
           <t>4、安全保密技术管理人员应对每日网络和系统运行情况实施安全审计，每月组织本级网络的安全性检测，编写安全审计与评估报告，并形成记录，系统配置发生变化的情况下应及时组织安全检测评估。</t>
         </is>
@@ -10307,12 +9705,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M137" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N137" s="5" t="inlineStr">
+      <c r="M137" s="0" t="inlineStr">
         <is>
           <t>需人工</t>
         </is>
@@ -10324,7 +9717,7 @@
           <t>协议安全审计</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr">
+      <c r="B138" s="0" t="inlineStr">
         <is>
           <t>审计协议的机密性、完整性、认可性、不可否认性</t>
         </is>
@@ -10379,36 +9772,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M138" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="N138" s="5" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="76" customHeight="1" s="11">
+      <c r="M138" s="0" t="inlineStr">
+        <is>
+          <t>需人工</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="76" customHeight="1" s="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="B139" s="10" t="inlineStr">
+      <c r="B139" s="7" t="inlineStr">
         <is>
           <t>数据库的Linux和Windows的命令行指令相同，作业书的上的命令行在Linux同样适用。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
     <mergeCell ref="A93:A115"/>
     <mergeCell ref="A30:A43"/>
-    <mergeCell ref="B139:M139"/>
-    <mergeCell ref="A1:M1"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="B139:L139"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A4:A29"/>
     <mergeCell ref="A130:A133"/>
     <mergeCell ref="A116:A124"/>
@@ -10420,7 +9808,6 @@
     <mergeCell ref="A44:A76"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="A125:A129"/>
-    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/配置核查表_v2.0.0_标注自动验证.xlsx
+++ b/配置核查表_v2.0.0_标注自动验证.xlsx
@@ -1252,6 +1252,7 @@
     <col width="86.95" customWidth="1" style="1" min="2" max="2"/>
     <col width="11.0833333333333" customWidth="1" style="1" min="4" max="4"/>
     <col width="9.449999999999999" customWidth="1" style="1" min="6" max="6"/>
+    <col width="55" customWidth="1" style="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="187" customHeight="1" s="1">
@@ -1352,7 +1353,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" s="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>系统安全</t>
@@ -1413,13 +1414,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M4" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、SQL Server、Nginx、Tomcat 组件脚本自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" s="1">
       <c r="B5" s="0" t="inlineStr">
         <is>
           <t>2、操作系统应安装防病毒软件并及时升级</t>
@@ -1475,13 +1476,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M5" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" s="1">
       <c r="B6" s="0" t="inlineStr">
         <is>
           <t>3、操作系统应按需求裁剪服务和端口</t>
@@ -1537,13 +1538,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M6" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" s="1">
       <c r="B7" s="0" t="inlineStr">
         <is>
           <t>4、操作系应身有防火墙功能</t>
@@ -1599,13 +1600,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M7" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" s="1">
       <c r="B8" s="0" t="inlineStr">
         <is>
           <t>5、操作系统应停用冗余网络设置</t>
@@ -1661,9 +1662,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M8" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
         </is>
       </c>
     </row>
@@ -1724,13 +1725,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M9" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" s="1">
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1" s="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>7、数据库管理系统应删除冗余帐户,应设置不少于8个字符且字符采用字母大小写，
@@ -1787,13 +1788,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M10" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" s="1">
       <c r="B11" s="0" t="inlineStr">
         <is>
           <t>8、数据库管理系统应删除冗余存储过程</t>
@@ -1849,13 +1850,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M11" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 MySQL、Redis、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" s="1">
       <c r="B12" s="0" t="inlineStr">
         <is>
           <t>9、数据库管理系统应具有基于表级增删改查等细粒度访问和管理授权功能</t>
@@ -1911,13 +1912,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M12" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 MySQL、达梦、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" s="1">
       <c r="B13" s="0" t="inlineStr">
         <is>
           <t>10、数据库管理系统应具有自主访问控制功能</t>
@@ -1973,13 +1974,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M13" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" s="1">
       <c r="B14" s="0" t="inlineStr">
         <is>
           <t>11、数据库管理系统应具有备份和恢复功能</t>
@@ -2035,13 +2036,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M14" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" s="1">
       <c r="B15" s="0" t="inlineStr">
         <is>
           <t>12、数据库管理系统应具有表级审计、告警和阻断功能</t>
@@ -2097,13 +2098,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M15" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" s="1">
       <c r="B16" s="0" t="inlineStr">
         <is>
           <t>13、数据库管理系统的数据应和其它应用的数据分类独立存储</t>
@@ -2159,13 +2160,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M16" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" s="1">
       <c r="B17" s="0" t="inlineStr">
         <is>
           <t>14、中间件应采取限制运行权限和使用安全管理通道等安全加固措施</t>
@@ -2221,13 +2222,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M17" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 Nginx、Tomcat 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" s="1">
       <c r="B18" s="0" t="inlineStr">
         <is>
           <t>15、应具备数据库管理系统超级管理员远程登录限制远程登陆限制能力</t>
@@ -2283,13 +2284,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M18" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" s="1">
       <c r="B19" s="0" t="inlineStr">
         <is>
           <t>16、应具备数据库管理系统输入（参数）检查能力</t>
@@ -2345,13 +2346,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M19" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（脚本无法判定应用层参数校验逻辑，需人工或 AWVS 类工具核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" s="1">
       <c r="B20" s="0" t="inlineStr">
         <is>
           <t>17、应限制操作系统开放的远程管理服务或端口</t>
@@ -2407,13 +2408,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M20" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" s="1">
       <c r="B21" s="0" t="inlineStr">
         <is>
           <t>18、应限制用户对服务器资源的最大或最小使用限度</t>
@@ -2469,13 +2470,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M21" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" s="1">
       <c r="B22" s="0" t="inlineStr">
         <is>
           <t>19、应更换数据库管理系统的默认服务端口、管理员用户名和口令</t>
@@ -2531,13 +2532,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M22" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" s="1">
       <c r="B23" s="5" t="inlineStr">
         <is>
           <t>20、数据库管理系统应配置安全策略</t>
@@ -2593,13 +2594,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M23" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 MySQL、Redis、达梦 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" s="1">
       <c r="B24" s="0" t="inlineStr">
         <is>
           <t>21、数据库管理系统应具有行级或列级审计功能</t>
@@ -2655,13 +2656,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M24" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 MySQL、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" s="1">
       <c r="B25" s="0" t="inlineStr">
         <is>
           <t>22、数据库管理系统应采取单独、安全监控、审计指施</t>
@@ -2717,13 +2718,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M25" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" s="1">
       <c r="B26" s="0" t="inlineStr">
         <is>
           <t>23、数据库管理系统仅为应用服务器提供访问服务</t>
@@ -2779,13 +2780,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M26" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" s="1">
       <c r="B27" s="0" t="inlineStr">
         <is>
           <t>24、应具备日志审计能力，审计日志至少保留180天</t>
@@ -2841,13 +2842,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M27" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL 组件脚本自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" s="1">
       <c r="B28" s="0" t="inlineStr">
         <is>
           <t>25、检查是否具备边界保护能力,是否可以抗攻击，防纂改</t>
@@ -2903,13 +2904,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M28" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" s="1">
       <c r="B29" s="0" t="inlineStr">
         <is>
           <t>26、检查是否有防病毒日志、补丁日志、记录相关信息 记录信息的完整，有效</t>
@@ -2965,13 +2966,13 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M29" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1" s="1">
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="50" customHeight="1" s="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>数据安全</t>
@@ -3032,13 +3033,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M30" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查 OS 层磁盘加密；数据库 TDE 需人工）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" s="1">
       <c r="B31" s="0" t="inlineStr">
         <is>
           <t>2、用户计算机之间的数据交互、文件传输凳应统一管控和审计</t>
@@ -3094,13 +3095,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M31" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" s="1">
       <c r="B32" s="0" t="inlineStr">
         <is>
           <t>3、涉密存储载体在降密级使用前或重大JS演训活动结束后，应采取数据写覆盖方法及时清除数据</t>
@@ -3156,13 +3157,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M32" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" s="1">
       <c r="B33" s="0" t="inlineStr">
         <is>
           <t>4、对确定销毁的涉密载体，应采取消磁、粉碎、溶解、化浆和熔化等方法进行销毁</t>
@@ -3218,9 +3219,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M33" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（载体销毁为物理过程，脚本不适用；需人工核查销毁档案与影像记录）</t>
         </is>
       </c>
     </row>
@@ -3280,13 +3281,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M34" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" s="1">
       <c r="B35" s="0" t="inlineStr">
         <is>
           <t>6、网络边界应具备信息过滤、敏感内容识别等数据放泄漏能力</t>
@@ -3342,9 +3343,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M35" s="0" t="inlineStr">
-        <is>
-          <t>跳过（不适用）</t>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查 DLP/终端管控客户端部署）</t>
         </is>
       </c>
     </row>
@@ -3404,13 +3405,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M36" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" s="1">
       <c r="B37" s="0" t="inlineStr">
         <is>
           <t>8、数据存储系统应根据重要程度划分不同存储区快，并设置用户访问权限</t>
@@ -3466,9 +3467,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M37" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
         </is>
       </c>
     </row>
@@ -3528,13 +3529,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M38" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" s="1">
       <c r="B39" s="0" t="inlineStr">
         <is>
           <t>10、检查数据共享是否合理，是否存在安全隐患</t>
@@ -3590,13 +3591,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M39" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" s="1">
       <c r="B40" s="0" t="inlineStr">
         <is>
           <t>11、检查对数据的访问是否按照权限分级访问，是否对访问行为进行审计</t>
@@ -3652,13 +3653,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M40" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" s="1">
       <c r="B41" s="0" t="inlineStr">
         <is>
           <t>12、检查数据采集是否超出业务需求范围</t>
@@ -3714,13 +3715,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M41" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（脚本可查采集/同步服务进程，采集范围与业务需求比对需人工）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" s="1">
       <c r="B42" s="0" t="inlineStr">
         <is>
           <t>13、检查数据各环节处理是否满足密级相应的保密要求</t>
@@ -3776,9 +3777,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M42" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
         </is>
       </c>
     </row>
@@ -3838,13 +3839,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M43" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（OS 层权限与审计可查，大数据平台统一管控需平台界面人工核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" s="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
           <t>应用安全</t>
@@ -3905,13 +3906,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M44" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（OS/数据库备份任务可查，应用自身备份功能需登录应用核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" s="1">
       <c r="B45" s="0" t="inlineStr">
         <is>
           <t>2、应用系统软件应及时安装补丁程序，且更新所用升级包应经过安全性测试；</t>
@@ -3967,13 +3968,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M45" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" s="1">
       <c r="B46" s="0" t="inlineStr">
         <is>
           <t>3、需基于可信根对应用系统软件进行可信验证。可信性受到破坏后报警。</t>
@@ -4029,13 +4030,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M46" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" s="1">
       <c r="B47" s="0" t="inlineStr">
         <is>
           <t>4、提供公共信息服务的服务器应应与涉密信息服务器分设，专用服务器应只提供专用服务。</t>
@@ -4091,13 +4092,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M47" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" s="1">
       <c r="B48" s="0" t="inlineStr">
         <is>
           <t>5、提供公共信息服务的服务器应具备防DDoS攻击能力</t>
@@ -4153,13 +4154,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M48" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 Nginx 组件脚本自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" s="1">
       <c r="B49" s="0" t="inlineStr">
         <is>
           <t>6、Web应用系统服务器应采取Web防护措施。</t>
@@ -4215,13 +4216,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M49" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 Nginx 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" s="1">
       <c r="B50" s="0" t="inlineStr">
         <is>
           <t>7、网站服务宜以静态页面形式发布；</t>
@@ -4277,13 +4278,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M50" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" s="1">
       <c r="B51" s="0" t="inlineStr">
         <is>
           <t>8、网站应采取网页放篡改措施，防止对信息内容的非法修改；</t>
@@ -4339,13 +4340,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M51" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 Nginx、Tomcat 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" s="1">
       <c r="B52" s="0" t="inlineStr">
         <is>
           <t>9、Web应用系统应具备防范SQL注入、跨站脚本等攻击能力；</t>
@@ -4401,13 +4402,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M52" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（curl 可查安全响应头，SQL注入/XSS防护能力需 WAF/代码审计）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" s="1">
       <c r="B53" s="0" t="inlineStr">
         <is>
           <t>10、Web应用系统应具备执行代码有效验证能力；</t>
@@ -4463,13 +4464,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M53" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（上传白名单等配置可查，执行代码校验需 nikto 扫描或人工）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" s="1">
       <c r="B54" s="0" t="inlineStr">
         <is>
           <t>11、应具备用户授权访问控制能力；</t>
@@ -4525,13 +4526,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M54" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" s="1">
       <c r="B55" s="0" t="inlineStr">
         <is>
           <t>12、应具备访问应用最大并发会话连接数限制能力；</t>
@@ -4587,13 +4588,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M55" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" s="1">
       <c r="B56" s="0" t="inlineStr">
         <is>
           <t>13、业务管理终端专设专用；</t>
@@ -4649,9 +4650,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M56" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（登录来源 IP 可比对，管理终端专设专用需现场核对台账）</t>
         </is>
       </c>
     </row>
@@ -4711,13 +4712,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M57" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" s="1">
       <c r="B58" s="0" t="inlineStr">
         <is>
           <t>15、文电等文档专用业务处理系统应具有签名验证、密级标识等功能；</t>
@@ -4773,13 +4774,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M58" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（证书工具安装状态可查，签名验证/密级标识功能需人工核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" s="1">
       <c r="B59" s="0" t="inlineStr">
         <is>
           <t>16、远程管理应采取加密保护措施；</t>
@@ -4835,9 +4836,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M59" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
         </is>
       </c>
     </row>
@@ -4897,13 +4898,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M60" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" s="1">
       <c r="B61" s="0" t="inlineStr">
         <is>
           <t>18、业务管理终端登录应采取网络地址限制措施；</t>
@@ -4959,13 +4960,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M61" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" s="1">
       <c r="B62" s="0" t="inlineStr">
         <is>
           <t>19、应具有结束会话、限定登录错误次数和自动退出等登录失败处理功能；</t>
@@ -5021,13 +5022,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M62" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" s="1">
       <c r="B63" s="0" t="inlineStr">
         <is>
           <t>20、宜使用自主设计开发的网络服务、协议、接口等，增强应用安全。</t>
@@ -5083,9 +5084,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M63" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（国密 SM2/3/4 配置可 grep，自主设计认定需人工）</t>
         </is>
       </c>
     </row>
@@ -5145,13 +5146,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M64" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（多因素与数字证书认证需人工核查 Windows Hello/国密证书库）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" s="1">
       <c r="B65" s="0" t="inlineStr">
         <is>
           <t>22、应更改Web应用系统默认服务发布端口；</t>
@@ -5207,13 +5208,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M65" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 Nginx、Tomcat 组件脚本自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" s="1">
       <c r="B66" s="0" t="inlineStr">
         <is>
           <t>23、应分开设置管理端口与应用端口；</t>
@@ -5269,13 +5270,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M66" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs 及 Tomcat 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" s="1">
       <c r="B67" s="0" t="inlineStr">
         <is>
           <t>24、应用服务和数据存储应部署在不同的服务器上；</t>
@@ -5331,9 +5332,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M67" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
         </is>
       </c>
     </row>
@@ -5393,13 +5394,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M68" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" s="1">
       <c r="B69" s="0" t="inlineStr">
         <is>
           <t>26、应经过代码级安全漏洞挖掘；</t>
@@ -5455,13 +5456,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M69" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1" s="1">
+      <c r="M69" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（代码级漏洞挖掘需渗透测试/代码审计工具，脚本不适用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="34" customHeight="1" s="1">
       <c r="B70" s="4" t="inlineStr">
         <is>
           <t>27、检查是否具备对人机接口输入、网络通信输入、文件输入的数据进行格式和长度检查的功能；</t>
@@ -5517,9 +5518,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M70" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（php upload_max_filesize 等校验配置可查，校验有效性需人工测试）</t>
         </is>
       </c>
     </row>
@@ -5579,13 +5580,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M71" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（curl 可查安全头，四类攻击防御能力需 WAF/渗透测试验证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" s="1">
       <c r="B72" s="0" t="inlineStr">
         <is>
           <t>29、检查是否具有用户访问权限统一管理功能；</t>
@@ -5641,13 +5642,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M72" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（统一权限管理平台需人工核查 IAM/SSO 接入与变更记录）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" s="1">
       <c r="B73" s="0" t="inlineStr">
         <is>
           <t>30、检查是否具备统一管理措施，是否对远程管理进行限制；</t>
@@ -5703,13 +5704,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M73" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" s="1">
       <c r="B74" s="0" t="inlineStr">
         <is>
           <t>31、检查是否能够设置最大并发会话连接数、会话建立速率、单用户并发会话数；</t>
@@ -5765,13 +5766,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M74" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_kylin.sh自动核查；Windows OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" s="1">
       <c r="B75" s="0" t="inlineStr">
         <is>
           <t>32、检查所有应用是否具备备份与恢复功能；</t>
@@ -5819,13 +5820,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M75" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" s="1">
       <c r="B76" s="0" t="inlineStr">
         <is>
           <t>33、检查应用软件是否基于国产自主可控软硬件自主开发</t>
@@ -5881,9 +5882,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M76" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
         </is>
       </c>
     </row>
@@ -5948,13 +5949,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M77" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" s="1">
       <c r="B78" s="0" t="inlineStr">
         <is>
           <t>2、用户计算机应根据需要安装补丁程序；</t>
@@ -6010,13 +6011,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M78" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" s="1">
       <c r="B79" s="0" t="inlineStr">
         <is>
           <t>3、用户应设置用户应用口令，通过认证后使用信息服务；</t>
@@ -6072,13 +6073,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M79" s="0" t="inlineStr">
-        <is>
-          <t>跳过（不适用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查自动登录/空口令账户限制）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" s="1">
       <c r="B80" s="0" t="inlineStr">
         <is>
           <t>4、用户计算机应具有互不相同的用户名和口令；</t>
@@ -6134,13 +6135,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M80" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" s="1">
       <c r="B81" s="0" t="inlineStr">
         <is>
           <t>5、用户计算机应关闭冗余系统服务和端口；</t>
@@ -6196,13 +6197,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M81" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
+      <c r="M81" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" s="1">
       <c r="B82" s="0" t="inlineStr">
         <is>
           <t>6、用户计算机应具备阻断和告警非法连接互联网的能力；</t>
@@ -6258,13 +6259,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M82" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" s="1">
       <c r="B83" s="0" t="inlineStr">
         <is>
           <t>7、用户计算机应具有文件保护功能；</t>
@@ -6320,9 +6321,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M83" s="0" t="inlineStr">
-        <is>
-          <t>跳过（不适用）</t>
+      <c r="M83" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查系统盘文件保护状态）</t>
         </is>
       </c>
     </row>
@@ -6382,13 +6383,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M84" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
+      <c r="M84" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" s="1">
       <c r="B85" s="0" t="inlineStr">
         <is>
           <t>9、用户计算机应禁止安装与工作无关的软件；</t>
@@ -6444,13 +6445,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M85" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
+      <c r="M85" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" s="1">
       <c r="B86" s="0" t="inlineStr">
         <is>
           <t>10、用户计算机USB接口应禁止私自连接对拷线和手机、媒体播放设备等个人移动电子设备；</t>
@@ -6506,9 +6507,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M86" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
         </is>
       </c>
     </row>
@@ -6568,9 +6569,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M87" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
+      <c r="M87" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
         </is>
       </c>
     </row>
@@ -6630,13 +6631,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M88" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" s="1">
       <c r="B89" s="0" t="inlineStr">
         <is>
           <t>13、用户计算机应采取非法外联阻断、文件输出管控等措施；</t>
@@ -6692,13 +6693,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M89" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
+      <c r="M89" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" s="1">
       <c r="B90" s="0" t="inlineStr">
         <is>
           <t>14、应具备用户行为审计能力；审计日志应至少保留xxd；</t>
@@ -6754,13 +6755,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M90" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" s="1">
       <c r="B91" s="0" t="inlineStr">
         <is>
           <t>15、检查安全策略配置情况和设置功能；</t>
@@ -6816,13 +6817,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M91" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="13" customHeight="1" s="1">
+      <c r="M91" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="50" customHeight="1" s="1">
       <c r="B92" s="0" t="inlineStr">
         <is>
           <t>16、检查被试装备中操作系统、数据库以及应用软件等是否完成补丁修复和升级到最新版本；</t>
@@ -6878,9 +6879,9 @@
           <t>√</t>
         </is>
       </c>
-      <c r="M92" s="0" t="inlineStr">
-        <is>
-          <t>可自动化</t>
+      <c r="M92" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、SQL Server 组件脚本自动核查）</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6951,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M93" s="0" t="inlineStr">
+      <c r="M93" s="4" t="inlineStr">
         <is>
           <t>需人工（台账/平台核查）</t>
         </is>
@@ -7019,7 +7020,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M94" s="0" t="inlineStr">
+      <c r="M94" s="4" t="inlineStr">
         <is>
           <t>需人工（台账/平台核查）</t>
         </is>
@@ -7081,9 +7082,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M95" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
+      <c r="M95" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
         </is>
       </c>
     </row>
@@ -7143,9 +7144,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M96" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
+      <c r="M96" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
         </is>
       </c>
     </row>
@@ -7205,9 +7206,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M97" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
+      <c r="M97" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
         </is>
       </c>
     </row>
@@ -7267,13 +7268,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M98" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" s="1">
       <c r="B99" s="0" t="inlineStr">
         <is>
           <t>7、网络设备应开放唯一网络管理服务，并限制管理终端访问</t>
@@ -7329,13 +7330,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M99" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
+      <c r="M99" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" s="1">
       <c r="B100" s="0" t="inlineStr">
         <is>
           <t>8、远程网络管理网络设备和网络安全防护设备应采用具有加密保护功能的管理服务</t>
@@ -7391,13 +7392,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M100" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" s="1">
       <c r="B101" s="0" t="inlineStr">
         <is>
           <t>9、同一网络传输链路具有相同安全功能的防护设备应使用不同架构或不同品牌产品</t>
@@ -7453,13 +7454,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M101" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化（脚本+台账）</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
+      <c r="M101" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（用 check_network.sh 提取设备型号，异构部署结论需比对台账）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" s="1">
       <c r="B102" s="0" t="inlineStr">
         <is>
           <t>10、应对组播源、组播地址、组播成员采取控制措施</t>
@@ -7515,13 +7516,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M102" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
+      <c r="M102" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" s="1">
       <c r="B103" s="0" t="inlineStr">
         <is>
           <t>11、重要网络设备和网络安全防护设备应有备份</t>
@@ -7577,13 +7578,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M103" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
+      <c r="M103" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" s="1">
       <c r="B104" s="0" t="inlineStr">
         <is>
           <t>12、远程传输应采取链路加密、网络加密、信源加密中两层保护措施</t>
@@ -7639,7 +7640,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M104" s="0" t="inlineStr">
+      <c r="M104" s="4" t="inlineStr">
         <is>
           <t>需人工（台账/平台核查）</t>
         </is>
@@ -7701,7 +7702,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M105" s="0" t="inlineStr">
+      <c r="M105" s="4" t="inlineStr">
         <is>
           <t>需人工（台账/平台核查）</t>
         </is>
@@ -7763,7 +7764,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M106" s="0" t="inlineStr">
+      <c r="M106" s="4" t="inlineStr">
         <is>
           <t>需人工（台账/平台核查）</t>
         </is>
@@ -7825,7 +7826,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M107" s="0" t="inlineStr">
+      <c r="M107" s="4" t="inlineStr">
         <is>
           <t>需人工（台账/平台核查）</t>
         </is>
@@ -7887,13 +7888,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M108" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" s="1">
       <c r="B109" s="0" t="inlineStr">
         <is>
           <t>17、远程传输租用地方线路时应采取链路加密、网络加密、信源加密三层保护措施</t>
@@ -7949,7 +7950,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M109" s="0" t="inlineStr">
+      <c r="M109" s="4" t="inlineStr">
         <is>
           <t>需人工（台账/平台核查）</t>
         </is>
@@ -8011,13 +8012,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M110" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" s="1">
       <c r="B111" s="0" t="inlineStr">
         <is>
           <t>19、用户计算机之间应逻辑隔离</t>
@@ -8073,13 +8074,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M111" s="0" t="inlineStr">
-        <is>
-          <t>可自动化（网络设备脚本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
+      <c r="M111" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_network.sh 采集设备回显后自动判定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" s="1">
       <c r="B112" s="0" t="inlineStr">
         <is>
           <t>20、应具备全网行为审计记录能力，审计日志应至少保留180天</t>
@@ -8135,13 +8136,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M112" s="0" t="inlineStr">
+      <c r="M112" s="4" t="inlineStr">
         <is>
           <t>需人工（台账/平台核查）</t>
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" s="1">
       <c r="B113" s="0" t="inlineStr">
         <is>
           <t>21、应对全网攻击行为、违规行为采取实时监视、报警、审计、控制处理、阻断和定位措施</t>
@@ -8197,13 +8198,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M113" s="0" t="inlineStr">
+      <c r="M113" s="4" t="inlineStr">
         <is>
           <t>需人工（台账/平台核查）</t>
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" s="1">
       <c r="B114" s="0" t="inlineStr">
         <is>
           <t>22、数据存储系统的管理网路与应用网路应逻辑隔离</t>
@@ -8259,13 +8260,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M114" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化（脚本+台账）</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（用 check_network.sh 提取存储网/业务网划分信号，结论需比对台账）</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" s="1">
       <c r="B115" s="0" t="inlineStr">
         <is>
           <t>23、检查网络设备配备的合理性、必要性，是否存在非必要的冗余内容</t>
@@ -8321,9 +8322,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M115" s="0" t="inlineStr">
-        <is>
-          <t>部分可自动化（脚本+台账）</t>
+      <c r="M115" s="4" t="inlineStr">
+        <is>
+          <t>部分可自动化（用 check_network.sh 计算端口闲置率，配备必要性结论需人工评估）</t>
         </is>
       </c>
     </row>
@@ -8388,13 +8389,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M116" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
+      <c r="M116" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" s="1">
       <c r="B117" s="0" t="inlineStr">
         <is>
           <t>2、使用的安全网关、防火墙等信息安全产品，应通过JD信息安全测评认证机构的认证</t>
@@ -8450,13 +8451,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M117" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
+      <c r="M117" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" s="1">
       <c r="B118" s="0" t="inlineStr">
         <is>
           <t>3、机房应有序、规范、合理走线布线，明确互联网区域和内部区域，粘贴标识，区分不同线路</t>
@@ -8512,13 +8513,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M118" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
+      <c r="M118" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" s="1">
       <c r="B119" s="0" t="inlineStr">
         <is>
           <t>4、机房应符合GB 2887-2011中4.6.1所规定的温湿度等要求</t>
@@ -8574,13 +8575,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M119" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
+      <c r="M119" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" s="1">
       <c r="B120" s="0" t="inlineStr">
         <is>
           <t>5、机房应安装安防监控设备，对机房的人员进出、设备操作等进行监管</t>
@@ -8636,13 +8637,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M120" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
+      <c r="M120" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" s="1">
       <c r="B121" s="0" t="inlineStr">
         <is>
           <t>6、机房应将涉密区域和互联网区域设置于不同场所</t>
@@ -8698,13 +8699,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M121" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
+      <c r="M121" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" s="1">
       <c r="B122" s="0" t="inlineStr">
         <is>
           <t>7、在涉密网络中使用过的打印机、复印机、刻录机、扫描仪、存储载体等设备严禁在互联网中使用</t>
@@ -8760,9 +8761,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M122" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
+      <c r="M122" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
         </is>
       </c>
     </row>
@@ -8822,13 +8823,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M123" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
+      <c r="M123" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" s="1">
       <c r="B124" s="0" t="inlineStr">
         <is>
           <t>9、与安全防护等级低的网络使用不同色系线缆进行严格隔离区分</t>
@@ -8884,13 +8885,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M124" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" s="1">
       <c r="A125" s="3" t="inlineStr">
         <is>
           <t>组织机构</t>
@@ -8951,13 +8952,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M125" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
+      <c r="M125" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" s="1">
       <c r="B126" s="0" t="inlineStr">
         <is>
           <t>2、应配备专职系统安全保密管理人员，负责系统安全措施的落实。</t>
@@ -9013,13 +9014,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M126" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" s="1">
       <c r="B127" s="0" t="inlineStr">
         <is>
           <t>3、应具有安全管理领导机构，督导系统安全措施的落实；</t>
@@ -9075,13 +9076,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M127" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
+      <c r="M127" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" s="1">
       <c r="B128" s="0" t="inlineStr">
         <is>
           <t>4、应具有系统安全保密技术管理人员，具体负责安全保密技术措施的落实，保证系统安全运行；</t>
@@ -9137,13 +9138,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M128" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
+      <c r="M128" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" s="1">
       <c r="B129" s="0" t="inlineStr">
         <is>
           <t>5、应具有完善的应急响应体系，应对突发事件。</t>
@@ -9199,13 +9200,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M129" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
+      <c r="M129" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" s="1">
       <c r="A130" s="3" t="inlineStr">
         <is>
           <t>规章制度</t>
@@ -9266,13 +9267,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M130" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
+      <c r="M130" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" s="1">
       <c r="B131" s="0" t="inlineStr">
         <is>
           <t>2、应具有安全管理操作规程、安全监控操作规程、安全审计操作规程、应急响应操作规程等。</t>
@@ -9328,13 +9329,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M131" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
+      <c r="M131" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" s="1">
       <c r="B132" s="0" t="inlineStr">
         <is>
           <t>3、应具有日常系统备份制度和存储载体使用管理制度；</t>
@@ -9390,13 +9391,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M132" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
+      <c r="M132" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" s="1">
       <c r="B133" s="0" t="inlineStr">
         <is>
           <t>4、应具有脆弱性分析等规程。</t>
@@ -9452,9 +9453,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M133" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
+      <c r="M133" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
         </is>
       </c>
     </row>
@@ -9519,9 +9520,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M134" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
+      <c r="M134" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
         </is>
       </c>
     </row>
@@ -9581,13 +9582,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M135" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
+      <c r="M135" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" s="1">
       <c r="B136" s="0" t="inlineStr">
         <is>
           <t>3、应具有与实际情况相符且完整的安全保密策略文档和安全保密技术及产品配置的详细记录；</t>
@@ -9643,9 +9644,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M136" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
+      <c r="M136" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
         </is>
       </c>
     </row>
@@ -9705,13 +9706,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M137" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
+      <c r="M137" s="4" t="inlineStr">
+        <is>
+          <t>需人工（现场/文档/台账类核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" s="1">
       <c r="A138" s="3" t="inlineStr">
         <is>
           <t>协议安全审计</t>
@@ -9772,9 +9773,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M138" s="0" t="inlineStr">
-        <is>
-          <t>需人工</t>
+      <c r="M138" s="4" t="inlineStr">
+        <is>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查 TLS/SSH 协议版本）</t>
         </is>
       </c>
     </row>

--- a/配置核查表_v2.0.0_标注自动验证.xlsx
+++ b/配置核查表_v2.0.0_标注自动验证.xlsx
@@ -1416,7 +1416,7 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、SQL Server、Nginx、Tomcat 组件脚本自动核查）</t>
+          <t>部分可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、SQL Server、Nginx、Tomcat 组件脚本 自动核查；达梦 需人工）</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>可自动化（用 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 MySQL、Redis、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 MySQL、Redis、SQL Server 组件脚本 自动核查；达梦 需人工）</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 MySQL、达梦、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>可自动化（用 MySQL、达梦、SQL Server 组件脚本自动核查）</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+          <t>可自动化（用 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+          <t>可自动化（用 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+          <t>可自动化（用 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（脚本输出数据库存储配置，分类独立存储与业务符合性需人工核对）</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 Nginx、Tomcat 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>可自动化（用 Nginx、Tomcat 组件脚本自动核查）</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+          <t>可自动化（用 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（脚本无法判定应用层参数校验逻辑，需人工或 AWVS 类工具核查）</t>
+          <t>部分可自动化（数据库脚本输出输入检查要点，参数化查询等应用层校验需 sqlmap/AWVS 或人工核查）</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+          <t>可自动化（用 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 MySQL、Redis、达梦 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 MySQL、Redis、达梦 组件脚本 自动核查；SQL Server 需人工）</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 MySQL、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 MySQL、SQL Server 组件脚本 自动核查；Redis、达梦 需人工）</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（脚本可查审计开关与参数，独立安全监护与审计措施需人工确认）</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>可自动化（用 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL 组件脚本自动核查）</t>
+          <t>部分可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL 组件脚本 自动核查；Redis、达梦、SQL Server 需人工）</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 及 MySQL、Redis、达梦、SQL Server 组件脚本 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、达梦、SQL Server 组件脚本 自动核查）</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查 OS 层磁盘加密；数据库 TDE 需人工）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查磁盘加密 BitLocker/LUKS）</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（OS/数据库备份任务可查，应用自身备份功能需登录应用核查）</t>
+          <t>部分可自动化（OS 定时备份任务可查，应用自身备份功能需登录应用核查）</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 Nginx 组件脚本自动核查）</t>
+          <t>部分可自动化（脚本可查服务与限流配置线索，防DDoS多层协同能力需人工/边界设备核查）</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 Nginx 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 Nginx、Tomcat 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 Nginx、Tomcat 组件脚本自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs 及 Tomcat 组件脚本自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_kylin.sh自动核查；Windows OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_kylin.sh 自动核查；Windows OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（脚本检测备份目录与备份文件，恢复能力需人工验证）</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查自动登录/空口令账户限制）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查自动登录与空口令账户限制）</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh自动核查）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查）</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs自动核查；麒麟 OS 层需人工确认）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、SQL Server 组件脚本自动核查）</t>
+          <t>部分可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、SQL Server 组件脚本 自动核查；达梦 需人工）</t>
         </is>
       </c>
     </row>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="M138" s="4" t="inlineStr">
         <is>
-          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查 TLS/SSH 协议版本）</t>
+          <t>可自动化（用 check_xp7.vbs、check_kylin.sh 自动核查 TLS/SSH 协议版本；协议层条目，勾选矩阵未单列对象）</t>
         </is>
       </c>
     </row>

--- a/配置核查表_v2.0.0_标注自动验证.xlsx
+++ b/配置核查表_v2.0.0_标注自动验证.xlsx
@@ -1416,7 +1416,7 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、SQL Server、Nginx、Tomcat 组件脚本 自动核查；达梦 需人工）</t>
+          <t>部分可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、SQL Server、Nginx、Tomcat 组件脚本自动核查；达梦脚本采集版本信息、补丁比对需人工）</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 MySQL、Redis、SQL Server 组件脚本 自动核查；达梦 需人工）</t>
+          <t>部分可自动化（用 MySQL、SQL Server、Redis 组件脚本自动核查；达梦脚本采集存储过程数量、冗余判定需人工）</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（脚本输出数据库存储配置，分类独立存储与业务符合性需人工核对）</t>
+          <t>需人工（脚本未执行检测，数据分类独立存储需结合业务架构人工核查）</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（数据库脚本输出输入检查要点，参数化查询等应用层校验需 sqlmap/AWVS 或人工核查）</t>
+          <t>需人工（应用层参数校验逻辑，脚本无法检测，需 sqlmap/AWVS 或代码审计）</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 MySQL、Redis、达梦 组件脚本 自动核查；SQL Server 需人工）</t>
+          <t>部分可自动化（用 MySQL、达梦、Redis 组件脚本自动核查；SQL Server 侧脚本未覆盖该项）</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 MySQL、SQL Server 组件脚本 自动核查；Redis、达梦 需人工）</t>
+          <t>部分可自动化（用 MySQL、SQL Server 组件脚本自动核查；达梦、Redis 侧审计粒度需人工核查）</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（脚本可查审计开关与参数，独立安全监护与审计措施需人工确认）</t>
+          <t>需人工（数据库独立安全监护与审计措施，脚本未执行检测）</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL 组件脚本 自动核查；Redis、达梦、SQL Server 需人工）</t>
+          <t>部分可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL 组件脚本自动核查；SQL Server、达梦、Redis 侧留存时长需人工核查）</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 及 MySQL、Redis、达梦、SQL Server 组件脚本 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（用 check_xp7.vbs 及 MySQL、SQL Server、达梦、Redis 组件脚本自动核查；麒麟侧需人工）</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（载体销毁为物理过程，脚本不适用；需人工核查销毁档案与影像记录）</t>
+          <t>需人工（载体物理销毁，脚本不适用；核查销毁档案与影像记录）</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟脚本检测分区划分、分级授权需人工核查）</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟脚本检测共享服务、目录权限需人工核查）</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（脚本可查采集/同步服务进程，采集范围与业务需求比对需人工）</t>
+          <t>需人工（采集范围与业务需求比对，脚本未执行检测）</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（OS 层权限与审计可查，大数据平台统一管控需平台界面人工核查）</t>
+          <t>需人工（大数据平台统一管控，需平台界面人工核查）</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（OS 定时备份任务可查，应用自身备份功能需登录应用核查）</t>
+          <t>部分可自动化（check_kylin.sh 检测备份配置与定时任务、备份有效性需人工确认；Windows 侧需人工）</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（脚本可查服务与限流配置线索，防DDoS多层协同能力需人工/边界设备核查）</t>
+          <t>需人工（防DDoS需边界设备核查，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟脚本检测 WAF 组件、应用层防护配置需人工核查）</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟脚本检测防篡改工具、Web 目录监控配置需人工确认）</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（curl 可查安全响应头，SQL注入/XSS防护能力需 WAF/代码审计）</t>
+          <t>需人工（SQL注入/XSS防护需 WAF/代码审计，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（上传白名单等配置可查，执行代码校验需 nikto 扫描或人工）</t>
+          <t>需人工（执行代码校验需 nikto 扫描或人工，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟脚本列出管理员组、RBAC 细粒度需人工核查）</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟侧需按指导书方法人工核查并发限制）</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（登录来源 IP 可比对，管理终端专设专用需现场核对台账）</t>
+          <t>需人工（管理终端专设专用需现场核对台账，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（证书工具安装状态可查，签名验证/密级标识功能需人工核查）</t>
+          <t>需人工（签名验证/密级标识功能需人工核查，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="34" customHeight="1" s="1">
+    <row r="60" ht="50" customHeight="1" s="1">
       <c r="B60" s="4" t="inlineStr">
         <is>
           <t>17、应支持管理员、安全员、审计员三权分立的职责划分，禁止设立超级管理员，并限制管理员、安全员、审计员的数量；</t>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟脚本统计 sudo 配置、三权分立划分需人工核查）</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（国密 SM2/3/4 配置可 grep，自主设计认定需人工）</t>
+          <t>需人工（自主协议/接口认定需人工核查，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（多因素与数字证书认证需人工核查 Windows Hello/国密证书库）</t>
+          <t>需人工（多因素与数字证书认证需人工核查，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟侧需人工核查管理端口与业务端口分离）</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟侧需人工核查应用与数据分离部署）</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（代码级漏洞挖掘需渗透测试/代码审计工具，脚本不适用）</t>
+          <t>需人工（代码级漏洞挖掘需渗透测试/代码审计，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（php upload_max_filesize 等校验配置可查，校验有效性需人工测试）</t>
+          <t>需人工（输入格式长度校验有效性需人工测试，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（curl 可查安全头，四类攻击防御能力需 WAF/渗透测试验证）</t>
+          <t>需人工（四类攻击防御能力需 WAF/渗透测试验证，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（统一权限管理平台需人工核查 IAM/SSO 接入与变更记录）</t>
+          <t>需人工（统一权限管理平台需人工核查 IAM/SSO，脚本仅输出方法提示）</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_kylin.sh 自动核查；Windows OS 层 需人工）</t>
+          <t>部分可自动化（check_kylin.sh 自动判定；Windows 侧需人工核查并发会话限制）</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（脚本检测备份目录与备份文件，恢复能力需人工验证）</t>
+          <t>部分可自动化（check_kylin.sh 检测备份目录/备份文件/定时任务、恢复能力需人工验证）</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟侧以 1.1 补丁核查结果为准、结合终端管理平台人工核实）</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟脚本统计自启服务数、多余服务判定需人工）</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟脚本统计网络连接数、违规外联判定需人工）</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟侧需人工确认终端管控软件部署）</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查；麒麟 OS 层 需人工）</t>
+          <t>部分可自动化（check_xp7.vbs 自动判定；麒麟侧需结合终端管理平台人工核查）</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、Redis、SQL Server 组件脚本 自动核查；达梦 需人工）</t>
+          <t>部分可自动化（用 check_xp7.vbs、check_kylin.sh 及 MySQL、SQL Server、Redis 组件脚本自动核查；达梦脚本采集版本、升级比对需人工）</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_network.sh 提取设备型号，异构部署结论需比对台账）</t>
+          <t>部分可自动化（check_network.sh 提取设备型号，异构部署结论需比对台账）</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>需人工（台账/平台核查）</t>
+          <t>部分可自动化（check_network.sh 采集 IKE SA 识别网络层加密，加密层次组合需按方案人工核对）</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7708,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="34" customHeight="1" s="1">
+    <row r="106" ht="50" customHeight="1" s="1">
       <c r="B106" s="4" t="inlineStr">
         <is>
           <t>14、与互联网、非JD网络、安全防护等级为一级的网络应物理隔离，与安全防护等级为二级、三级和四级的网络应逻辑隔离</t>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>需人工（台账/平台核查）</t>
+          <t>部分可自动化（check_network.sh 核对防火墙会话表比对跨域通道，隔离方式与等级对应需人工核查）</t>
         </is>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="M109" s="4" t="inlineStr">
         <is>
-          <t>需人工（台账/平台核查）</t>
+          <t>部分可自动化（check_network.sh 采集 IKE SA 识别网络层加密，链路层/信源层加密需按方案人工核对）</t>
         </is>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_network.sh 提取存储网/业务网划分信号，结论需比对台账）</t>
+          <t>部分可自动化（check_network.sh 提取存储网/业务网 VLAN 划分信号，结论需比对台账）</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_network.sh 计算端口闲置率，配备必要性结论需人工评估）</t>
+          <t>可自动化（用 check_network.sh 采集端口状态并计算闲置率自动判定；配备必要性可结合台账复核）</t>
         </is>
       </c>
     </row>

--- a/配置核查表_v2.0.0_标注自动验证.xlsx
+++ b/配置核查表_v2.0.0_标注自动验证.xlsx
@@ -1257,9 +1257,17 @@
   <cols>
     <col width="23.3083333333333" customWidth="1" style="1" min="1" max="1"/>
     <col width="86.95" customWidth="1" style="1" min="2" max="2"/>
-    <col width="11.0833333333333" customWidth="1" style="1" min="4" max="4"/>
-    <col width="9.449999999999999" customWidth="1" style="1" min="6" max="6"/>
-    <col width="55" customWidth="1" style="1" min="13" max="13"/>
+    <col width="11" customWidth="1" style="1" min="3" max="3"/>
+    <col width="11" customWidth="1" style="1" min="4" max="4"/>
+    <col width="11" customWidth="1" style="1" min="5" max="5"/>
+    <col width="11" customWidth="1" style="1" min="6" max="6"/>
+    <col width="11" customWidth="1" style="1" min="7" max="7"/>
+    <col width="11" customWidth="1" style="1" min="8" max="8"/>
+    <col width="11" customWidth="1" style="1" min="9" max="9"/>
+    <col width="11" customWidth="1" style="1" min="10" max="10"/>
+    <col width="11" customWidth="1" style="1" min="11" max="11"/>
+    <col width="11" customWidth="1" style="1" min="12" max="12"/>
+    <col width="11" customWidth="1" style="1" min="13" max="13"/>
     <col width="55" customWidth="1" style="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1711,7 +1719,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" s="1">
+    <row r="9" ht="36" customHeight="1" s="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>6、操作系统远程管理应开放唯一管理服务,指定管理终端
@@ -1779,7 +1787,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="50" customHeight="1" s="1">
+    <row r="10" ht="81" customHeight="1" s="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>7、数据库管理系统应删除冗余帐户,应设置不少于8个字符且字符采用字母大小写，
@@ -3120,7 +3128,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="50" customHeight="1" s="1">
+    <row r="30" ht="96" customHeight="1" s="1">
       <c r="B30" s="0" t="inlineStr">
         <is>
           <t>27、操作系统、数据库管理系统、中间件、办公软件等基础软件应采用具有完备的售后技术支持与服务的正版或定制软件</t>
@@ -3393,7 +3401,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="34" customHeight="1" s="1">
+    <row r="34" ht="36" customHeight="1" s="1">
       <c r="B34" s="0" t="inlineStr">
         <is>
           <t>4、对确定销毁的涉密载体，应采取消磁、粉碎、溶解、化浆和熔化等方法进行销毁</t>
@@ -3527,7 +3535,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="50" customHeight="1" s="1">
+    <row r="36" ht="66" customHeight="1" s="1">
       <c r="B36" s="0" t="inlineStr">
         <is>
           <t>6、网络边界应具备信息过滤、敏感内容识别等数据放泄漏能力</t>
@@ -3661,7 +3669,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="50" customHeight="1" s="1">
+    <row r="38" ht="51" customHeight="1" s="1">
       <c r="B38" s="0" t="inlineStr">
         <is>
           <t>8、数据存储系统应根据重要程度划分不同存储区快，并设置用户访问权限</t>
@@ -3996,7 +4004,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="50" customHeight="1" s="1">
+    <row r="43" ht="51" customHeight="1" s="1">
       <c r="B43" s="0" t="inlineStr">
         <is>
           <t>13、检查数据各环节处理是否满足密级相应的保密要求</t>
@@ -4939,7 +4947,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="34" customHeight="1" s="1">
+    <row r="57" ht="36" customHeight="1" s="1">
       <c r="B57" s="0" t="inlineStr">
         <is>
           <t>13、业务管理终端专设专用；</t>
@@ -5140,7 +5148,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="50" customHeight="1" s="1">
+    <row r="60" ht="66" customHeight="1" s="1">
       <c r="B60" s="0" t="inlineStr">
         <is>
           <t>16、远程管理应采取加密保护措施；</t>
@@ -5408,7 +5416,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="34" customHeight="1" s="1">
+    <row r="64" ht="36" customHeight="1" s="1">
       <c r="B64" s="0" t="inlineStr">
         <is>
           <t>20、宜使用自主设计开发的网络服务、协议、接口等，增强应用安全。</t>
@@ -5676,7 +5684,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="50" customHeight="1" s="1">
+    <row r="68" ht="51" customHeight="1" s="1">
       <c r="B68" s="0" t="inlineStr">
         <is>
           <t>24、应用服务和数据存储应部署在不同的服务器上；</t>
@@ -5810,7 +5818,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="34" customHeight="1" s="1">
+    <row r="70" ht="36" customHeight="1" s="1">
       <c r="B70" s="0" t="inlineStr">
         <is>
           <t>26、应经过代码级安全漏洞挖掘；</t>
@@ -5877,7 +5885,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="34" customHeight="1" s="1">
+    <row r="71" ht="36" customHeight="1" s="1">
       <c r="B71" s="4" t="inlineStr">
         <is>
           <t>27、检查是否具备对人机接口输入、网络通信输入、文件输入的数据进行格式和长度检查的功能；</t>
@@ -6279,7 +6287,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="34" customHeight="1" s="1">
+    <row r="77" ht="36" customHeight="1" s="1">
       <c r="B77" s="0" t="inlineStr">
         <is>
           <t>33、检查应用软件是否基于国产自主可控软硬件自主开发</t>
@@ -6753,7 +6761,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="34" customHeight="1" s="1">
+    <row r="84" ht="36" customHeight="1" s="1">
       <c r="B84" s="0" t="inlineStr">
         <is>
           <t>7、用户计算机应具有文件保护功能；</t>
@@ -7021,7 +7029,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="34" customHeight="1" s="1">
+    <row r="88" ht="36" customHeight="1" s="1">
       <c r="B88" s="4" t="inlineStr">
         <is>
           <t>11、用户计算机登录应使用基于专用物理部件或生物特征的多因素身份认证方式，应设置超时锁屏，屏幕保护等待时间不超过5min,服务器应设置登录口令，口令超度不得少于10个字符，字符应采用字母大小写、数字及特殊字符混合编制，更换周期不超过30d;</t>
@@ -7574,7 +7582,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="50" customHeight="1" s="1">
+    <row r="96" ht="51" customHeight="1" s="1">
       <c r="B96" s="4" t="inlineStr">
         <is>
           <t>3、应按最小化原则设计网络架构，局域网宜采用交换技术组网，在适当预留扩展空间的前提下合理配置连续IP地址</t>
@@ -7641,7 +7649,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="50" customHeight="1" s="1">
+    <row r="97" ht="51" customHeight="1" s="1">
       <c r="B97" s="4" t="inlineStr">
         <is>
           <t>4、网络边界物理互联的节点数量、使用的路由协议种类、用于路由的地址网段等应满足最小化原则</t>
@@ -7708,7 +7716,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="50" customHeight="1" s="1">
+    <row r="98" ht="51" customHeight="1" s="1">
       <c r="B98" s="4" t="inlineStr">
         <is>
           <t>5、局域网内部应根据业务性质划分若干个安全区域，不同用途的服务器、数据存储设备、除网络设备外的嵌入式设备应单独划分安全区域</t>
@@ -8177,7 +8185,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="50" customHeight="1" s="1">
+    <row r="105" ht="51" customHeight="1" s="1">
       <c r="B105" s="0" t="inlineStr">
         <is>
           <t>12、远程传输应采取链路加密、网络加密、信源加密中两层保护措施</t>
@@ -8512,7 +8520,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="50" customHeight="1" s="1">
+    <row r="110" ht="51" customHeight="1" s="1">
       <c r="B110" s="0" t="inlineStr">
         <is>
           <t>17、远程传输租用地方线路时应采取链路加密、网络加密、信源加密三层保护措施</t>
@@ -8914,7 +8922,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="50" customHeight="1" s="1">
+    <row r="116" ht="51" customHeight="1" s="1">
       <c r="B116" s="0" t="inlineStr">
         <is>
           <t>23、检查网络设备配备的合理性、必要性，是否存在非必要的冗余内容</t>
@@ -10563,10 +10571,10 @@
   <mergeCells count="16">
     <mergeCell ref="A131:A134"/>
     <mergeCell ref="A117:A125"/>
+    <mergeCell ref="B140:N140"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="A126:A130"/>
     <mergeCell ref="A135:A138"/>
-    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A4:A29"/>
     <mergeCell ref="A78:A93"/>
     <mergeCell ref="B2:B3"/>
@@ -10575,8 +10583,8 @@
     <mergeCell ref="A31:A44"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="A45:A77"/>
-    <mergeCell ref="B140:L140"/>
     <mergeCell ref="A94:A116"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/配置核查表_v2.0.0_标注自动验证.xlsx
+++ b/配置核查表_v2.0.0_标注自动验证.xlsx
@@ -8662,12 +8662,12 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>√</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>√</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_network.sh / check_network.ps1 自动核查；check_kylin.sh 未执行该项检测，需人工核查）</t>
+          <t>部分可自动化（用 check_network.sh / check_network.ps1 自动核查；check_xp7.vbs、check_kylin.sh 未执行该项检测，需人工核查）</t>
         </is>
       </c>
     </row>
@@ -10568,20 +10568,21 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A131:A134"/>
+    <mergeCell ref="A4:A30"/>
     <mergeCell ref="A117:A125"/>
     <mergeCell ref="B140:N140"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="A126:A130"/>
     <mergeCell ref="A135:A138"/>
-    <mergeCell ref="A4:A29"/>
     <mergeCell ref="A78:A93"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="N2:N3"/>
     <mergeCell ref="A31:A44"/>
     <mergeCell ref="C2:F2"/>
+    <mergeCell ref="A2:A3"/>
     <mergeCell ref="A45:A77"/>
     <mergeCell ref="A94:A116"/>
     <mergeCell ref="A1:N1"/>

--- a/配置核查表_v2.0.0_标注自动验证.xlsx
+++ b/配置核查表_v2.0.0_标注自动验证.xlsx
@@ -1851,7 +1851,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs、check_mysql、check_sqlserver、check_dm、check_redis 自动核查；check_kylin.sh 未执行该项检测，需人工核查）</t>
+          <t>部分可自动化（用 check_xp7.vbs、check_mysql、check_sqlserver、check_dm、check_redis 自动核查；用 check_kylin.sh 采集检测结果、结论需人工确认）</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 及 MySQL、SQL Server、Redis 组件脚本自动核查；达梦脚本采集存储过程数量、冗余判定需人工；麒麟脚本未执行该项检测）</t>
+          <t>部分可自动化（用 check_xp7.vbs 及 MySQL、SQL Server、Redis 组件脚本自动核查；check_dm 采集存储过程数量，check_kylin.sh 检测数据库服务运行状态，账户与冗余判定需人工核查）</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs、check_mysql、check_sqlserver、check_dm 自动核查；check_kylin.sh、check_redis 未执行该项检测，需人工核查）</t>
+          <t>部分可自动化（用 check_xp7.vbs、check_mysql、check_sqlserver、check_dm 自动核查；用 check_kylin.sh 采集检测结果、结论需人工确认；check_redis 未执行该项检测，需人工核查）</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 连接 MySQL 自动核查多库混用情况；麒麟及各数据库脚本未执行该项检测，需人工核查）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查多库混用情况；check_kylin.sh 检测数据库服务运行状态，MySQL、SQL Server、达梦侧脚本未执行该项检测，分类独立存储需人工核查）</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 及 MySQL、达梦、Redis 组件脚本自动核查；SQL Server、麒麟侧脚本未执行该项检测）</t>
+          <t>部分可自动化（用 check_xp7.vbs 及 MySQL、达梦、Redis 组件脚本自动核查；check_kylin.sh 检测数据库服务运行状态，SQL Server 侧脚本未执行该项检测，安全策略明细需人工核查）</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 及 MySQL、SQL Server 组件脚本自动核查；达梦、Redis 侧审计粒度需人工核查；麒麟脚本未执行该项检测）</t>
+          <t>部分可自动化（用 check_xp7.vbs 及 MySQL、SQL Server 组件脚本自动核查；check_kylin.sh 检测数据库服务运行状态，达梦、Redis 侧审计粒度需人工核查）</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs 自动核查 MySQL binlog 日志保留天数；麒麟及 SQL Server、达梦、Redis 侧未执行该项检测，需人工核查）</t>
+          <t>部分可自动化（用 check_xp7.vbs 自动核查本机 MySQL binlog 日志保留天数；check_kylin.sh 检测数据库服务运行状态，SQL Server、达梦、Redis 侧脚本未执行该项检测，留存时长与独立监控需人工核查）</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>部分可自动化（用 check_xp7.vbs、check_mysql、check_sqlserver、check_dm、check_redis 自动核查；check_kylin.sh 未执行该项检测，需人工核查）</t>
+          <t>部分可自动化（用 check_xp7.vbs、check_mysql、check_sqlserver、check_dm、check_redis 自动核查；用 check_kylin.sh 采集检测结果、结论需人工确认）</t>
         </is>
       </c>
     </row>
